--- a/Week 3/DAB_Sorting_Filtering_Exercises.xlsx
+++ b/Week 3/DAB_Sorting_Filtering_Exercises.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ab76ec252c957cd7/Desktop/data_bootcamp_folder/instructor_ref/instructor_ref/Week 3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37AC3A18-FD44-4C34-9014-F1AA4670E853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="44" documentId="13_ncr:1_{37AC3A18-FD44-4C34-9014-F1AA4670E853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCA2F291-CD64-4E64-BA9F-5E4CE4185A29}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Practice_Data" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,9 @@
     <sheet name="Sol_AND_Logic" sheetId="7" r:id="rId7"/>
     <sheet name="Sol_OR_Logic" sheetId="8" r:id="rId8"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Practice_Data!$A$1:$F$13</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -1195,6 +1198,10 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1480,19 +1487,50 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="525" row="0">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{8328831D-CA30-449B-B7AC-4DF534A62820}">
+  <we:reference id="wa200007447" version="1.1.6.7" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200007447" version="1.1.6.7" store="" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+  <we:extLst>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{D87F86FE-615C-45B5-9D79-34F1136793EB}">
+      <we:containsCustomFunctions/>
+    </a:ext>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{7C84B067-C214-45C3-A712-C9D94CD141B2}">
+      <we:customFunctionIdList>
+        <we:customFunctionIds>_xldudf_BOARDFLARE_EXEC</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_BOARDFLARE_RUNPY</we:customFunctionIds>
+      </we:customFunctionIdList>
+    </a:ext>
+  </we:extLst>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
     <col min="5" max="5" width="7" customWidth="1"/>
-    <col min="6" max="6" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1512,167 +1550,167 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>1001</v>
+        <v>1012</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
         <v>7</v>
       </c>
       <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2">
+        <v>2000</v>
+      </c>
+      <c r="F2" s="2">
+        <v>46016</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>1001</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
         <v>8</v>
       </c>
-      <c r="E2">
+      <c r="E3">
         <v>1200</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F3" s="2">
         <v>46143</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>1002</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>1010</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
         <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3">
-        <v>450</v>
-      </c>
-      <c r="F3" s="2">
-        <v>46144</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>1003</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
       </c>
       <c r="D4" t="s">
         <v>8</v>
       </c>
       <c r="E4">
+        <v>1100</v>
+      </c>
+      <c r="F4" s="2">
+        <v>46032</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>1007</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5">
+        <v>950</v>
+      </c>
+      <c r="F5" s="2">
+        <v>46149</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>1003</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6">
         <v>800</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F6" s="2">
         <v>46127</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>1004</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" t="s">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>1005</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7">
+        <v>600</v>
+      </c>
+      <c r="F7" s="2">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>1008</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" t="s">
         <v>14</v>
       </c>
-      <c r="D5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5">
-        <v>150</v>
-      </c>
-      <c r="F5" s="2">
-        <v>46146</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>1005</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="D8" t="s">
         <v>11</v>
       </c>
-      <c r="E6">
-        <v>600</v>
-      </c>
-      <c r="F6" s="2">
-        <v>46147</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>1006</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="E8">
+        <v>500</v>
+      </c>
+      <c r="F8" s="2">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>1002</v>
+      </c>
+      <c r="B9" t="s">
         <v>9</v>
       </c>
-      <c r="C7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7">
-        <v>200</v>
-      </c>
-      <c r="F7" s="2">
-        <v>46101</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>1007</v>
-      </c>
-      <c r="B8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="C9" t="s">
         <v>10</v>
-      </c>
-      <c r="D8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8">
-        <v>950</v>
-      </c>
-      <c r="F8" s="2">
-        <v>46149</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>1008</v>
-      </c>
-      <c r="B9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" t="s">
-        <v>14</v>
       </c>
       <c r="D9" t="s">
         <v>11</v>
       </c>
       <c r="E9">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="F9" s="2">
-        <v>46150</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+        <v>46144</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>1009</v>
       </c>
@@ -1692,67 +1730,71 @@
         <v>46151</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>1010</v>
+        <v>1006</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E11">
-        <v>1100</v>
+        <v>200</v>
       </c>
       <c r="F11" s="2">
-        <v>46032</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+        <v>46101</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>1011</v>
+        <v>1004</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="C12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D12" t="s">
         <v>15</v>
       </c>
       <c r="E12">
+        <v>150</v>
+      </c>
+      <c r="F12" s="2">
+        <v>46146</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>1011</v>
+      </c>
+      <c r="B13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13">
         <v>50</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F13" s="2">
         <v>46152</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>1012</v>
-      </c>
-      <c r="B13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13">
-        <v>2000</v>
-      </c>
-      <c r="F13" s="2">
-        <v>46016</v>
-      </c>
-    </row>
   </sheetData>
+  <autoFilter ref="A1:F13" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F13">
+    <sortCondition ref="D2:D13" customList="Eletronics,Office Supplies,Furniture"/>
+  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1760,7 +1802,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
@@ -1768,7 +1810,7 @@
     <col min="5" max="5" width="63" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>18</v>
       </c>
@@ -1785,7 +1827,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1802,7 +1844,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1819,7 +1861,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1836,7 +1878,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1853,7 +1895,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1870,7 +1912,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1887,7 +1929,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>31</v>
       </c>
@@ -1901,7 +1943,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>31</v>
       </c>
@@ -1915,7 +1957,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>51</v>
       </c>
@@ -1929,7 +1971,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>55</v>
       </c>
@@ -1943,7 +1985,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>55</v>
       </c>
@@ -1965,7 +2007,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21543250-EB44-471E-A18F-2C2F3C53D912}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -1975,14 +2017,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACEB3746-2303-46AD-9209-3E74BEBA089D}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="52" customWidth="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>64</v>
       </c>
@@ -1993,7 +2035,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>67</v>
       </c>
@@ -2004,7 +2046,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>70</v>
       </c>
@@ -2015,7 +2057,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>73</v>
       </c>
@@ -2026,7 +2068,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>76</v>
       </c>
@@ -2037,7 +2079,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>79</v>
       </c>
@@ -2056,7 +2098,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F76EC7CC-86B1-42D5-9094-0D5585BE00DF}">
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
@@ -2065,7 +2107,7 @@
     <col min="6" max="6" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2085,7 +2127,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1012</v>
       </c>
@@ -2105,7 +2147,7 @@
         <v>46016</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1001</v>
       </c>
@@ -2125,7 +2167,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1010</v>
       </c>
@@ -2153,7 +2195,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04BD39B8-3359-48BD-A726-744363C91B5C}">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
@@ -2162,7 +2204,7 @@
     <col min="6" max="6" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2182,7 +2224,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1001</v>
       </c>
@@ -2202,7 +2244,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1003</v>
       </c>
@@ -2222,7 +2264,7 @@
         <v>46127</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1007</v>
       </c>
@@ -2242,7 +2284,7 @@
         <v>46149</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1010</v>
       </c>
@@ -2262,7 +2304,7 @@
         <v>46032</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>1012</v>
       </c>
@@ -2290,7 +2332,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9859671-17A3-480A-92C8-07861B53C67B}">
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
@@ -2299,7 +2341,7 @@
     <col min="6" max="6" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2319,7 +2361,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1001</v>
       </c>
@@ -2339,7 +2381,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1005</v>
       </c>
@@ -2359,7 +2401,7 @@
         <v>46147</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1012</v>
       </c>
@@ -2387,7 +2429,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{971A5F41-26BF-4063-AC61-19CA0189FB13}">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
@@ -2396,7 +2438,7 @@
     <col min="6" max="6" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2416,7 +2458,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1001</v>
       </c>
@@ -2436,7 +2478,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1003</v>
       </c>
@@ -2456,7 +2498,7 @@
         <v>46127</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1007</v>
       </c>
@@ -2476,7 +2518,7 @@
         <v>46149</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1010</v>
       </c>
@@ -2496,7 +2538,7 @@
         <v>46032</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>1011</v>
       </c>
